--- a/data/cv.xlsx
+++ b/data/cv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/CV/cv_qmd/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{9BB66F3E-D59C-482A-A609-DEFDD81AF93C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D8D91AA-985A-4B28-A9E0-225FDDF1472E}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{9BB66F3E-D59C-482A-A609-DEFDD81AF93C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F606529-2E4D-43DA-9BF3-9D1F2348A015}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1" t="s">
-        <v>35</v>
+        <v>884</v>
       </c>
     </row>
     <row r="6" spans="1:7">

--- a/data/cv.xlsx
+++ b/data/cv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/CV/cv_qmd/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="112" documentId="6_{E5D22C43-2D08-43EB-952F-DDB414BB7B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58047A57-76A1-4395-B155-659E4FD9E18E}"/>
+  <xr:revisionPtr revIDLastSave="140" documentId="6_{E5D22C43-2D08-43EB-952F-DDB414BB7B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE4BC914-B00A-4529-B5E1-467A3DE155C8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
     <sheet name="declarations" sheetId="11" r:id="rId11"/>
     <sheet name="review" sheetId="12" r:id="rId12"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0" forceFullCalc="1"/>
+  <calcPr calcId="191029" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4019" uniqueCount="1468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4036" uniqueCount="1473">
   <si>
     <t>CV workbook</t>
   </si>
@@ -4449,6 +4449,21 @@
   </si>
   <si>
     <t>Toffalini, E; Feraco, T.</t>
+  </si>
+  <si>
+    <t>pub_052</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.lindif.2026.102988</t>
+  </si>
+  <si>
+    <t>Pellegrino G, Feraco T., Meneghetti C, Carretti B. (2026). Social, emotional, and behavioral skills as resources for student engagement: A one-year longitudinal study in high school students. *Learning and Individual Differences*, *131*, 102988. [https://doi.org/10.1016/j.lindif.2026.102988](https://doi.org/10.1016/j.lindif.2026.102988).</t>
+  </si>
+  <si>
+    <t>https://osf.io/hrws7</t>
+  </si>
+  <si>
+    <t>Pellegrino, G; Feraco, T.; Meneghetti, C.; Carretti, B.</t>
   </si>
 </sst>
 </file>
@@ -4538,7 +4553,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -4580,12 +4595,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Collegamento ipertestuale" xfId="2" builtinId="8"/>
@@ -4986,9 +4998,9 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="PublicationsTable" displayName="PublicationsTable" ref="A1:U52" dataDxfId="41">
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U52">
-    <sortCondition ref="A1:A52"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="PublicationsTable" displayName="PublicationsTable" ref="A1:U53" dataDxfId="41">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U53">
+    <sortCondition ref="A1:A53"/>
   </sortState>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="publication_id" dataDxfId="40"/>
@@ -13152,7 +13164,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:U52"/>
+  <dimension ref="A1:U53"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -13233,131 +13245,126 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="17" customFormat="1">
-      <c r="A2" s="17" t="s">
+    <row r="2" spans="1:21" s="16" customFormat="1">
+      <c r="A2" s="16" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B2" s="17">
+        <v>52</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>901</v>
+      </c>
+      <c r="D2" s="17">
+        <v>2026</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>974</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>1469</v>
+      </c>
+      <c r="I2" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="K2" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="L2" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="O2" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="P2" s="15"/>
+      <c r="Q2" s="15" t="s">
+        <v>1471</v>
+      </c>
+      <c r="S2" s="15" t="s">
+        <v>1471</v>
+      </c>
+      <c r="T2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="U2" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" s="16" customFormat="1">
+      <c r="A3" s="16" t="s">
         <v>1465</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B3" s="17">
         <v>51</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C3" s="17" t="s">
         <v>901</v>
       </c>
-      <c r="D2" s="18">
+      <c r="D3" s="17">
         <v>2026</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E3" s="16" t="s">
         <v>1466</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F3" s="16" t="s">
         <v>1466</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G3" t="s">
         <v>1463</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="H3" s="15" t="s">
         <v>1464</v>
       </c>
-      <c r="I2" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="M2" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="P2" s="19"/>
-      <c r="T2" s="17" t="s">
+      <c r="I3" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="M3" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="N3" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="O3" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="P3" s="15"/>
+      <c r="T3" s="16" t="s">
         <v>1467</v>
       </c>
-      <c r="U2" s="17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21">
-      <c r="A3" t="s">
-        <v>1177</v>
-      </c>
-      <c r="B3" s="7">
-        <v>50</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>901</v>
-      </c>
-      <c r="D3" s="7">
-        <v>2026</v>
-      </c>
-      <c r="E3" t="s">
-        <v>1439</v>
-      </c>
-      <c r="F3" t="s">
-        <v>1439</v>
-      </c>
-      <c r="G3" t="s">
-        <v>1449</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>902</v>
-      </c>
-      <c r="I3" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K3" t="s">
-        <v>39</v>
-      </c>
-      <c r="L3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M3" t="s">
-        <v>39</v>
-      </c>
-      <c r="N3" t="s">
-        <v>39</v>
-      </c>
-      <c r="O3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P3" s="12" t="s">
-        <v>903</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>904</v>
-      </c>
-      <c r="R3" t="s">
-        <v>904</v>
-      </c>
-      <c r="S3" t="s">
-        <v>904</v>
-      </c>
-      <c r="T3" t="s">
-        <v>905</v>
-      </c>
-      <c r="U3" t="s">
+      <c r="U3" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:21">
       <c r="A4" t="s">
-        <v>1171</v>
+        <v>1177</v>
       </c>
       <c r="B4" s="7">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>901</v>
@@ -13365,64 +13372,64 @@
       <c r="D4" s="7">
         <v>2026</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>907</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>907</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>908</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>909</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>910</v>
-      </c>
-      <c r="Q4" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="R4" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="S4" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="T4" s="8" t="s">
-        <v>912</v>
-      </c>
-      <c r="U4" s="7" t="s">
+      <c r="E4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1449</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>902</v>
+      </c>
+      <c r="I4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K4" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s">
+        <v>39</v>
+      </c>
+      <c r="N4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O4" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="12" t="s">
+        <v>903</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>904</v>
+      </c>
+      <c r="R4" t="s">
+        <v>904</v>
+      </c>
+      <c r="S4" t="s">
+        <v>904</v>
+      </c>
+      <c r="T4" t="s">
+        <v>905</v>
+      </c>
+      <c r="U4" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:21">
       <c r="A5" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="B5" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>901</v>
@@ -13431,46 +13438,52 @@
         <v>2026</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>915</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>916</v>
+        <v>908</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>909</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="M5" s="7" t="s">
         <v>39</v>
       </c>
       <c r="N5" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="O5" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="12" t="s">
-        <v>917</v>
-      </c>
-      <c r="R5" s="7"/>
-      <c r="S5" s="7"/>
+        <v>39</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>910</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>911</v>
+      </c>
       <c r="T5" s="8" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="U5" s="7" t="s">
         <v>39</v>
@@ -13478,10 +13491,10 @@
     </row>
     <row r="6" spans="1:21">
       <c r="A6" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="B6" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>901</v>
@@ -13490,31 +13503,31 @@
         <v>2026</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>921</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>922</v>
+        <v>915</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>916</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="L6" s="7" t="s">
         <v>53</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="N6" s="7" t="s">
         <v>53</v>
@@ -13523,11 +13536,13 @@
         <v>53</v>
       </c>
       <c r="P6" s="7"/>
-      <c r="Q6" s="7"/>
+      <c r="Q6" s="12" t="s">
+        <v>917</v>
+      </c>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="8" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="U6" s="7" t="s">
         <v>39</v>
@@ -13535,10 +13550,10 @@
     </row>
     <row r="7" spans="1:21">
       <c r="A7" t="s">
-        <v>1155</v>
+        <v>1161</v>
       </c>
       <c r="B7" s="7">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>901</v>
@@ -13547,16 +13562,16 @@
         <v>2026</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>925</v>
+        <v>920</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>921</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>39</v>
@@ -13568,31 +13583,23 @@
         <v>39</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="N7" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="O7" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="P7" s="9" t="s">
-        <v>927</v>
-      </c>
-      <c r="Q7" s="7" t="s">
-        <v>928</v>
-      </c>
-      <c r="R7" s="7" t="s">
-        <v>928</v>
-      </c>
-      <c r="S7" s="7" t="s">
-        <v>928</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
       <c r="T7" s="8" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="U7" s="7" t="s">
         <v>39</v>
@@ -13600,10 +13607,10 @@
     </row>
     <row r="8" spans="1:21">
       <c r="A8" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="B8" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>901</v>
@@ -13612,25 +13619,25 @@
         <v>2026</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>932</v>
+        <v>921</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>933</v>
+        <v>926</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="L8" s="7" t="s">
         <v>39</v>
@@ -13644,20 +13651,20 @@
       <c r="O8" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P8" s="15" t="s">
-        <v>1440</v>
+      <c r="P8" s="9" t="s">
+        <v>927</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="R8" s="7" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="S8" s="7" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="T8" s="8" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="U8" s="7" t="s">
         <v>39</v>
@@ -13665,10 +13672,10 @@
     </row>
     <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="B9" s="7">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>901</v>
@@ -13677,16 +13684,16 @@
         <v>2026</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>53</v>
@@ -13698,27 +13705,31 @@
         <v>53</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="M9" s="7" t="s">
         <v>39</v>
       </c>
       <c r="N9" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="O9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="12" t="s">
-        <v>940</v>
-      </c>
-      <c r="R9" s="7"/>
-      <c r="S9" s="12" t="s">
-        <v>940</v>
+      <c r="P9" s="15" t="s">
+        <v>1440</v>
+      </c>
+      <c r="Q9" s="7" t="s">
+        <v>934</v>
+      </c>
+      <c r="R9" s="7" t="s">
+        <v>934</v>
+      </c>
+      <c r="S9" s="7" t="s">
+        <v>934</v>
       </c>
       <c r="T9" s="8" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="U9" s="7" t="s">
         <v>39</v>
@@ -13726,10 +13737,10 @@
     </row>
     <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
       <c r="B10" s="7">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>901</v>
@@ -13738,22 +13749,22 @@
         <v>2026</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="I10" s="7" t="s">
         <v>53</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="K10" s="7" t="s">
         <v>53</v>
@@ -13768,16 +13779,18 @@
         <v>53</v>
       </c>
       <c r="O10" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="P10" s="7"/>
-      <c r="Q10" s="7" t="s">
-        <v>946</v>
+      <c r="Q10" s="12" t="s">
+        <v>940</v>
       </c>
       <c r="R10" s="7"/>
-      <c r="S10" s="7"/>
+      <c r="S10" s="12" t="s">
+        <v>940</v>
+      </c>
       <c r="T10" s="8" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="U10" s="7" t="s">
         <v>39</v>
@@ -13785,10 +13798,10 @@
     </row>
     <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>1132</v>
+        <v>1137</v>
       </c>
       <c r="B11" s="7">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>901</v>
@@ -13797,16 +13810,16 @@
         <v>2026</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>53</v>
@@ -13821,7 +13834,7 @@
         <v>53</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="N11" s="7" t="s">
         <v>53</v>
@@ -13830,11 +13843,13 @@
         <v>53</v>
       </c>
       <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
+      <c r="Q11" s="7" t="s">
+        <v>946</v>
+      </c>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
       <c r="T11" s="8" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="U11" s="7" t="s">
         <v>39</v>
@@ -13842,28 +13857,28 @@
     </row>
     <row r="12" spans="1:21">
       <c r="A12" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
       <c r="B12" s="7">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>901</v>
       </c>
       <c r="D12" s="7">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>908</v>
+        <v>950</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>53</v>
@@ -13872,34 +13887,26 @@
         <v>39</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="O12" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="P12" s="9" t="s">
-        <v>956</v>
-      </c>
-      <c r="Q12" s="7" t="s">
-        <v>957</v>
-      </c>
-      <c r="R12" s="7" t="s">
-        <v>957</v>
-      </c>
-      <c r="S12" s="7" t="s">
-        <v>957</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
       <c r="T12" s="8" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="U12" s="7" t="s">
         <v>39</v>
@@ -13907,10 +13914,10 @@
     </row>
     <row r="13" spans="1:21">
       <c r="A13" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="B13" s="7">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>901</v>
@@ -13919,19 +13926,19 @@
         <v>2025</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>961</v>
+        <v>908</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>962</v>
+        <v>955</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>39</v>
@@ -13951,20 +13958,20 @@
       <c r="O13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P13" s="7" t="s">
-        <v>963</v>
+      <c r="P13" s="9" t="s">
+        <v>956</v>
       </c>
       <c r="Q13" s="7" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
       <c r="R13" s="7" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
       <c r="S13" s="7" t="s">
-        <v>964</v>
+        <v>957</v>
       </c>
       <c r="T13" s="8" t="s">
-        <v>965</v>
+        <v>958</v>
       </c>
       <c r="U13" s="7" t="s">
         <v>39</v>
@@ -13972,10 +13979,10 @@
     </row>
     <row r="14" spans="1:21">
       <c r="A14" t="s">
-        <v>1117</v>
+        <v>1122</v>
       </c>
       <c r="B14" s="7">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>901</v>
@@ -13984,28 +13991,28 @@
         <v>2025</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>967</v>
+        <v>960</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>967</v>
+        <v>960</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>968</v>
+        <v>961</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>39</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>39</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="M14" s="7" t="s">
         <v>39</v>
@@ -14016,18 +14023,20 @@
       <c r="O14" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P14" s="7"/>
+      <c r="P14" s="7" t="s">
+        <v>963</v>
+      </c>
       <c r="Q14" s="7" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="R14" s="7" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="S14" s="7" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="T14" s="8" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="U14" s="7" t="s">
         <v>39</v>
@@ -14035,10 +14044,10 @@
     </row>
     <row r="15" spans="1:21">
       <c r="A15" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="B15" s="7">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>901</v>
@@ -14047,44 +14056,50 @@
         <v>2025</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="J15" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="L15" s="7" t="s">
         <v>53</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="N15" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="O15" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="P15" s="7"/>
-      <c r="Q15" s="7"/>
-      <c r="R15" s="7"/>
-      <c r="S15" s="7"/>
+      <c r="Q15" s="7" t="s">
+        <v>970</v>
+      </c>
+      <c r="R15" s="7" t="s">
+        <v>970</v>
+      </c>
+      <c r="S15" s="7" t="s">
+        <v>970</v>
+      </c>
       <c r="T15" s="8" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="U15" s="7" t="s">
         <v>39</v>
@@ -14092,10 +14107,10 @@
     </row>
     <row r="16" spans="1:21">
       <c r="A16" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="B16" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>901</v>
@@ -14104,16 +14119,16 @@
         <v>2025</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>53</v>
@@ -14131,21 +14146,17 @@
         <v>53</v>
       </c>
       <c r="N16" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="O16" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
-      <c r="R16" s="7" t="s">
-        <v>981</v>
-      </c>
-      <c r="S16" s="7" t="s">
-        <v>981</v>
-      </c>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
       <c r="T16" s="8" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="U16" s="7" t="s">
         <v>39</v>
@@ -14153,10 +14164,10 @@
     </row>
     <row r="17" spans="1:21">
       <c r="A17" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="B17" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>901</v>
@@ -14165,16 +14176,16 @@
         <v>2025</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>53</v>
@@ -14189,7 +14200,7 @@
         <v>53</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="N17" s="7" t="s">
         <v>39</v>
@@ -14198,17 +14209,15 @@
         <v>39</v>
       </c>
       <c r="P17" s="7"/>
-      <c r="Q17" s="7" t="s">
-        <v>987</v>
-      </c>
+      <c r="Q17" s="7"/>
       <c r="R17" s="7" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="S17" s="7" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
       <c r="T17" s="8" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="U17" s="7" t="s">
         <v>39</v>
@@ -14216,10 +14225,10 @@
     </row>
     <row r="18" spans="1:21">
       <c r="A18" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="B18" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>901</v>
@@ -14228,50 +14237,50 @@
         <v>2025</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="M18" s="7" t="s">
         <v>39</v>
       </c>
       <c r="N18" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="O18" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P18" s="7" t="s">
-        <v>993</v>
-      </c>
+      <c r="P18" s="7"/>
       <c r="Q18" s="7" t="s">
-        <v>993</v>
-      </c>
-      <c r="R18" s="7"/>
+        <v>987</v>
+      </c>
+      <c r="R18" s="7" t="s">
+        <v>987</v>
+      </c>
       <c r="S18" s="7" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="T18" s="8" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="U18" s="7" t="s">
         <v>39</v>
@@ -14279,10 +14288,10 @@
     </row>
     <row r="19" spans="1:21">
       <c r="A19" t="s">
-        <v>1092</v>
+        <v>1097</v>
       </c>
       <c r="B19" s="7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>901</v>
@@ -14291,28 +14300,28 @@
         <v>2025</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>915</v>
+        <v>991</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>39</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="K19" s="7" t="s">
         <v>39</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="M19" s="7" t="s">
         <v>39</v>
@@ -14323,16 +14332,18 @@
       <c r="O19" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P19" s="7"/>
+      <c r="P19" s="7" t="s">
+        <v>993</v>
+      </c>
       <c r="Q19" s="7" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="R19" s="7"/>
       <c r="S19" s="7" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="T19" s="8" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="U19" s="7" t="s">
         <v>39</v>
@@ -14340,10 +14351,10 @@
     </row>
     <row r="20" spans="1:21">
       <c r="A20" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="B20" s="7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>901</v>
@@ -14352,16 +14363,16 @@
         <v>2025</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>1002</v>
+        <v>915</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>39</v>
@@ -14379,23 +14390,21 @@
         <v>39</v>
       </c>
       <c r="N20" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="O20" s="7" t="s">
         <v>39</v>
       </c>
       <c r="P20" s="7"/>
       <c r="Q20" s="7" t="s">
-        <v>1004</v>
-      </c>
-      <c r="R20" s="7" t="s">
-        <v>1004</v>
-      </c>
+        <v>998</v>
+      </c>
+      <c r="R20" s="7"/>
       <c r="S20" s="7" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="T20" s="8" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="U20" s="7" t="s">
         <v>39</v>
@@ -14403,10 +14412,10 @@
     </row>
     <row r="21" spans="1:21">
       <c r="A21" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="B21" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>901</v>
@@ -14415,22 +14424,22 @@
         <v>2025</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>39</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>39</v>
@@ -14449,16 +14458,16 @@
       </c>
       <c r="P21" s="7"/>
       <c r="Q21" s="7" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="R21" s="7" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="S21" s="7" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="T21" s="8" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="U21" s="7" t="s">
         <v>39</v>
@@ -14466,10 +14475,10 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="B22" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>901</v>
@@ -14478,25 +14487,25 @@
         <v>2025</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="J22" s="7" t="s">
         <v>39</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="L22" s="7" t="s">
         <v>53</v>
@@ -14505,19 +14514,23 @@
         <v>39</v>
       </c>
       <c r="N22" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="O22" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="P22" s="7"/>
       <c r="Q22" s="7" t="s">
-        <v>1016</v>
-      </c>
-      <c r="R22" s="7"/>
-      <c r="S22" s="7"/>
+        <v>1010</v>
+      </c>
+      <c r="R22" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="S22" s="7" t="s">
+        <v>1010</v>
+      </c>
       <c r="T22" s="8" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="U22" s="7" t="s">
         <v>39</v>
@@ -14525,10 +14538,10 @@
     </row>
     <row r="23" spans="1:21">
       <c r="A23" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
       <c r="B23" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>901</v>
@@ -14537,22 +14550,22 @@
         <v>2025</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>53</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>53</v>
@@ -14561,7 +14574,7 @@
         <v>53</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="N23" s="7" t="s">
         <v>53</v>
@@ -14570,11 +14583,13 @@
         <v>53</v>
       </c>
       <c r="P23" s="7"/>
-      <c r="Q23" s="7"/>
+      <c r="Q23" s="7" t="s">
+        <v>1016</v>
+      </c>
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
       <c r="T23" s="8" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="U23" s="7" t="s">
         <v>39</v>
@@ -14582,10 +14597,10 @@
     </row>
     <row r="24" spans="1:21">
       <c r="A24" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="B24" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>901</v>
@@ -14594,31 +14609,31 @@
         <v>2025</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J24" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="L24" s="7" t="s">
         <v>53</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="N24" s="7" t="s">
         <v>53</v>
@@ -14627,13 +14642,11 @@
         <v>53</v>
       </c>
       <c r="P24" s="7"/>
-      <c r="Q24" s="10" t="s">
-        <v>1027</v>
-      </c>
+      <c r="Q24" s="7"/>
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
       <c r="T24" s="8" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="U24" s="7" t="s">
         <v>39</v>
@@ -14641,43 +14654,43 @@
     </row>
     <row r="25" spans="1:21">
       <c r="A25" t="s">
-        <v>1054</v>
+        <v>1061</v>
       </c>
       <c r="B25" s="7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>901</v>
       </c>
       <c r="D25" s="7">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="J25" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="L25" s="7" t="s">
         <v>53</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="N25" s="7" t="s">
         <v>53</v>
@@ -14686,11 +14699,13 @@
         <v>53</v>
       </c>
       <c r="P25" s="7"/>
-      <c r="Q25" s="7"/>
+      <c r="Q25" s="10" t="s">
+        <v>1027</v>
+      </c>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
       <c r="T25" s="8" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="U25" s="7" t="s">
         <v>39</v>
@@ -14698,10 +14713,10 @@
     </row>
     <row r="26" spans="1:21">
       <c r="A26" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="B26" s="7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>901</v>
@@ -14710,25 +14725,25 @@
         <v>2024</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>53</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="L26" s="7" t="s">
         <v>53</v>
@@ -14747,7 +14762,7 @@
       <c r="R26" s="7"/>
       <c r="S26" s="7"/>
       <c r="T26" s="8" t="s">
-        <v>958</v>
+        <v>1033</v>
       </c>
       <c r="U26" s="7" t="s">
         <v>39</v>
@@ -14755,10 +14770,10 @@
     </row>
     <row r="27" spans="1:21">
       <c r="A27" t="s">
-        <v>1044</v>
+        <v>1050</v>
       </c>
       <c r="B27" s="7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>901</v>
@@ -14767,22 +14782,22 @@
         <v>2024</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="I27" s="7" t="s">
         <v>53</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="K27" s="7" t="s">
         <v>39</v>
@@ -14794,21 +14809,17 @@
         <v>53</v>
       </c>
       <c r="N27" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="O27" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="P27" s="7"/>
       <c r="Q27" s="7"/>
-      <c r="R27" s="7" t="s">
-        <v>1042</v>
-      </c>
-      <c r="S27" s="7" t="s">
-        <v>1042</v>
-      </c>
+      <c r="R27" s="7"/>
+      <c r="S27" s="7"/>
       <c r="T27" s="8" t="s">
-        <v>1043</v>
+        <v>958</v>
       </c>
       <c r="U27" s="7" t="s">
         <v>39</v>
@@ -14816,10 +14827,10 @@
     </row>
     <row r="28" spans="1:21">
       <c r="A28" t="s">
-        <v>1038</v>
+        <v>1044</v>
       </c>
       <c r="B28" s="7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>901</v>
@@ -14828,22 +14839,22 @@
         <v>2024</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="K28" s="7" t="s">
         <v>39</v>
@@ -14852,22 +14863,24 @@
         <v>53</v>
       </c>
       <c r="M28" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="N28" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="O28" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="P28" s="7"/>
-      <c r="Q28" s="7" t="s">
-        <v>1048</v>
-      </c>
-      <c r="R28" s="7"/>
-      <c r="S28" s="7"/>
+      <c r="Q28" s="7"/>
+      <c r="R28" s="7" t="s">
+        <v>1042</v>
+      </c>
+      <c r="S28" s="7" t="s">
+        <v>1042</v>
+      </c>
       <c r="T28" s="8" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="U28" s="7" t="s">
         <v>39</v>
@@ -14875,10 +14888,10 @@
     </row>
     <row r="29" spans="1:21">
       <c r="A29" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="B29" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>901</v>
@@ -14887,22 +14900,22 @@
         <v>2024</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>1036</v>
+        <v>1046</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>39</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="K29" s="7" t="s">
         <v>39</v>
@@ -14911,7 +14924,7 @@
         <v>53</v>
       </c>
       <c r="M29" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="N29" s="7" t="s">
         <v>53</v>
@@ -14920,11 +14933,13 @@
         <v>53</v>
       </c>
       <c r="P29" s="7"/>
-      <c r="Q29" s="7"/>
+      <c r="Q29" s="7" t="s">
+        <v>1048</v>
+      </c>
       <c r="R29" s="7"/>
       <c r="S29" s="7"/>
       <c r="T29" s="8" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="U29" s="7" t="s">
         <v>39</v>
@@ -14932,10 +14947,10 @@
     </row>
     <row r="30" spans="1:21">
       <c r="A30" t="s">
-        <v>1029</v>
+        <v>1034</v>
       </c>
       <c r="B30" s="7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>901</v>
@@ -14944,52 +14959,44 @@
         <v>2024</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>1056</v>
+        <v>1036</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="I30" s="7" t="s">
         <v>39</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="K30" s="7" t="s">
         <v>39</v>
       </c>
       <c r="L30" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="M30" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="N30" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="O30" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="P30" s="10" t="s">
-        <v>1058</v>
-      </c>
-      <c r="Q30" s="10" t="s">
-        <v>1059</v>
-      </c>
-      <c r="R30" s="10" t="s">
-        <v>1059</v>
-      </c>
-      <c r="S30" s="10" t="s">
-        <v>1059</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="P30" s="7"/>
+      <c r="Q30" s="7"/>
+      <c r="R30" s="7"/>
+      <c r="S30" s="7"/>
       <c r="T30" s="8" t="s">
-        <v>1060</v>
+        <v>1053</v>
       </c>
       <c r="U30" s="7" t="s">
         <v>39</v>
@@ -14997,10 +15004,10 @@
     </row>
     <row r="31" spans="1:21">
       <c r="A31" t="s">
-        <v>1023</v>
+        <v>1029</v>
       </c>
       <c r="B31" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>901</v>
@@ -15009,16 +15016,16 @@
         <v>2024</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>1062</v>
+        <v>1055</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>1063</v>
+        <v>1056</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>1064</v>
+        <v>1057</v>
       </c>
       <c r="I31" s="7" t="s">
         <v>39</v>
@@ -15030,27 +15037,31 @@
         <v>39</v>
       </c>
       <c r="L31" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="M31" s="7" t="s">
         <v>39</v>
       </c>
       <c r="N31" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="O31" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="P31" s="7"/>
-      <c r="Q31" s="7" t="s">
-        <v>1065</v>
-      </c>
-      <c r="R31" s="7"/>
-      <c r="S31" s="7" t="s">
-        <v>1066</v>
+      <c r="P31" s="10" t="s">
+        <v>1058</v>
+      </c>
+      <c r="Q31" s="10" t="s">
+        <v>1059</v>
+      </c>
+      <c r="R31" s="10" t="s">
+        <v>1059</v>
+      </c>
+      <c r="S31" s="10" t="s">
+        <v>1059</v>
       </c>
       <c r="T31" s="8" t="s">
-        <v>1067</v>
+        <v>1060</v>
       </c>
       <c r="U31" s="7" t="s">
         <v>39</v>
@@ -15058,28 +15069,28 @@
     </row>
     <row r="32" spans="1:21">
       <c r="A32" t="s">
-        <v>1018</v>
+        <v>1023</v>
       </c>
       <c r="B32" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>901</v>
       </c>
       <c r="D32" s="7">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>1069</v>
+        <v>1062</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1069</v>
+        <v>1062</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>1070</v>
+        <v>1063</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>1071</v>
+        <v>1064</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>39</v>
@@ -15094,7 +15105,7 @@
         <v>53</v>
       </c>
       <c r="M32" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="N32" s="7" t="s">
         <v>53</v>
@@ -15103,13 +15114,15 @@
         <v>39</v>
       </c>
       <c r="P32" s="7"/>
-      <c r="Q32" s="7"/>
+      <c r="Q32" s="7" t="s">
+        <v>1065</v>
+      </c>
       <c r="R32" s="7"/>
       <c r="S32" s="7" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="T32" s="8" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="U32" s="7" t="s">
         <v>39</v>
@@ -15117,10 +15130,10 @@
     </row>
     <row r="33" spans="1:21">
       <c r="A33" t="s">
-        <v>1012</v>
+        <v>1018</v>
       </c>
       <c r="B33" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>901</v>
@@ -15129,16 +15142,16 @@
         <v>2023</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="I33" s="7" t="s">
         <v>39</v>
@@ -15147,28 +15160,28 @@
         <v>39</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="L33" s="7" t="s">
         <v>53</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="N33" s="7" t="s">
         <v>53</v>
       </c>
       <c r="O33" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="P33" s="7"/>
-      <c r="Q33" s="7" t="s">
-        <v>1078</v>
-      </c>
+      <c r="Q33" s="7"/>
       <c r="R33" s="7"/>
-      <c r="S33" s="7"/>
+      <c r="S33" s="7" t="s">
+        <v>1072</v>
+      </c>
       <c r="T33" s="8" t="s">
-        <v>1079</v>
+        <v>1073</v>
       </c>
       <c r="U33" s="7" t="s">
         <v>39</v>
@@ -15176,10 +15189,10 @@
     </row>
     <row r="34" spans="1:21">
       <c r="A34" t="s">
-        <v>1006</v>
+        <v>1012</v>
       </c>
       <c r="B34" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>901</v>
@@ -15188,31 +15201,31 @@
         <v>2023</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>39</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="K34" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="L34" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="M34" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="N34" s="7" t="s">
         <v>53</v>
@@ -15220,14 +15233,14 @@
       <c r="O34" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="P34" s="7" t="s">
-        <v>1084</v>
-      </c>
-      <c r="Q34" s="7"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7" t="s">
+        <v>1078</v>
+      </c>
       <c r="R34" s="7"/>
       <c r="S34" s="7"/>
       <c r="T34" s="8" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="U34" s="7" t="s">
         <v>39</v>
@@ -15235,10 +15248,10 @@
     </row>
     <row r="35" spans="1:21">
       <c r="A35" t="s">
-        <v>1000</v>
+        <v>1006</v>
       </c>
       <c r="B35" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>901</v>
@@ -15247,31 +15260,31 @@
         <v>2023</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="I35" s="7" t="s">
         <v>39</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="K35" s="7" t="s">
         <v>39</v>
       </c>
       <c r="L35" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="M35" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="N35" s="7" t="s">
         <v>53</v>
@@ -15279,14 +15292,14 @@
       <c r="O35" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="P35" s="7"/>
-      <c r="Q35" s="7" t="s">
-        <v>1090</v>
-      </c>
+      <c r="P35" s="7" t="s">
+        <v>1084</v>
+      </c>
+      <c r="Q35" s="7"/>
       <c r="R35" s="7"/>
       <c r="S35" s="7"/>
       <c r="T35" s="8" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="U35" s="7" t="s">
         <v>39</v>
@@ -15294,10 +15307,10 @@
     </row>
     <row r="36" spans="1:21">
       <c r="A36" t="s">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="B36" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>901</v>
@@ -15306,22 +15319,22 @@
         <v>2023</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="I36" s="7" t="s">
         <v>39</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="K36" s="7" t="s">
         <v>39</v>
@@ -15340,12 +15353,12 @@
       </c>
       <c r="P36" s="7"/>
       <c r="Q36" s="7" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="R36" s="7"/>
       <c r="S36" s="7"/>
       <c r="T36" s="8" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="U36" s="7" t="s">
         <v>39</v>
@@ -15353,10 +15366,10 @@
     </row>
     <row r="37" spans="1:21">
       <c r="A37" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="B37" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>901</v>
@@ -15365,16 +15378,16 @@
         <v>2023</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>1099</v>
+        <v>1082</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>39</v>
@@ -15399,12 +15412,12 @@
       </c>
       <c r="P37" s="7"/>
       <c r="Q37" s="7" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
       <c r="R37" s="7"/>
       <c r="S37" s="7"/>
       <c r="T37" s="8" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
       <c r="U37" s="7" t="s">
         <v>39</v>
@@ -15412,10 +15425,10 @@
     </row>
     <row r="38" spans="1:21">
       <c r="A38" t="s">
-        <v>983</v>
+        <v>989</v>
       </c>
       <c r="B38" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>901</v>
@@ -15424,16 +15437,16 @@
         <v>2023</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="I38" s="7" t="s">
         <v>39</v>
@@ -15458,12 +15471,12 @@
       </c>
       <c r="P38" s="7"/>
       <c r="Q38" s="7" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="R38" s="7"/>
       <c r="S38" s="7"/>
       <c r="T38" s="8" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="U38" s="7" t="s">
         <v>39</v>
@@ -15471,10 +15484,10 @@
     </row>
     <row r="39" spans="1:21">
       <c r="A39" t="s">
-        <v>977</v>
+        <v>983</v>
       </c>
       <c r="B39" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>901</v>
@@ -15483,16 +15496,16 @@
         <v>2023</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>1105</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
       <c r="I39" s="7" t="s">
         <v>39</v>
@@ -15517,12 +15530,12 @@
       </c>
       <c r="P39" s="7"/>
       <c r="Q39" s="7" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="R39" s="7"/>
       <c r="S39" s="7"/>
       <c r="T39" s="8" t="s">
-        <v>1091</v>
+        <v>1108</v>
       </c>
       <c r="U39" s="7" t="s">
         <v>39</v>
@@ -15530,28 +15543,28 @@
     </row>
     <row r="40" spans="1:21">
       <c r="A40" t="s">
-        <v>972</v>
+        <v>977</v>
       </c>
       <c r="B40" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>901</v>
       </c>
       <c r="D40" s="7">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>1115</v>
+        <v>1105</v>
       </c>
       <c r="H40" s="7" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>39</v>
@@ -15566,7 +15579,7 @@
         <v>53</v>
       </c>
       <c r="M40" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="N40" s="7" t="s">
         <v>53</v>
@@ -15575,11 +15588,13 @@
         <v>53</v>
       </c>
       <c r="P40" s="7"/>
-      <c r="Q40" s="7"/>
+      <c r="Q40" s="7" t="s">
+        <v>1112</v>
+      </c>
       <c r="R40" s="7"/>
       <c r="S40" s="7"/>
       <c r="T40" s="8" t="s">
-        <v>1053</v>
+        <v>1091</v>
       </c>
       <c r="U40" s="7" t="s">
         <v>39</v>
@@ -15587,10 +15602,10 @@
     </row>
     <row r="41" spans="1:21">
       <c r="A41" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="B41" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>901</v>
@@ -15599,16 +15614,16 @@
         <v>2022</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="I41" s="7" t="s">
         <v>39</v>
@@ -15623,7 +15638,7 @@
         <v>53</v>
       </c>
       <c r="M41" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="N41" s="7" t="s">
         <v>53</v>
@@ -15632,13 +15647,11 @@
         <v>53</v>
       </c>
       <c r="P41" s="7"/>
-      <c r="Q41" s="7" t="s">
-        <v>1121</v>
-      </c>
+      <c r="Q41" s="7"/>
       <c r="R41" s="7"/>
       <c r="S41" s="7"/>
       <c r="T41" s="8" t="s">
-        <v>1091</v>
+        <v>1053</v>
       </c>
       <c r="U41" s="7" t="s">
         <v>39</v>
@@ -15646,10 +15659,10 @@
     </row>
     <row r="42" spans="1:21">
       <c r="A42" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="B42" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C42" s="7" t="s">
         <v>901</v>
@@ -15658,16 +15671,16 @@
         <v>2022</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
       <c r="I42" s="7" t="s">
         <v>39</v>
@@ -15691,13 +15704,13 @@
         <v>53</v>
       </c>
       <c r="P42" s="7"/>
-      <c r="Q42" s="9" t="s">
-        <v>1126</v>
+      <c r="Q42" s="7" t="s">
+        <v>1121</v>
       </c>
       <c r="R42" s="7"/>
       <c r="S42" s="7"/>
       <c r="T42" s="8" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="U42" s="7" t="s">
         <v>39</v>
@@ -15705,10 +15718,10 @@
     </row>
     <row r="43" spans="1:21">
       <c r="A43" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
       <c r="B43" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C43" s="7" t="s">
         <v>901</v>
@@ -15717,16 +15730,16 @@
         <v>2022</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="I43" s="7" t="s">
         <v>39</v>
@@ -15750,13 +15763,13 @@
         <v>53</v>
       </c>
       <c r="P43" s="7"/>
-      <c r="Q43" s="12" t="s">
-        <v>1131</v>
+      <c r="Q43" s="9" t="s">
+        <v>1126</v>
       </c>
       <c r="R43" s="7"/>
       <c r="S43" s="7"/>
       <c r="T43" s="8" t="s">
-        <v>1108</v>
+        <v>1085</v>
       </c>
       <c r="U43" s="7" t="s">
         <v>39</v>
@@ -15764,10 +15777,10 @@
     </row>
     <row r="44" spans="1:21">
       <c r="A44" t="s">
-        <v>948</v>
+        <v>953</v>
       </c>
       <c r="B44" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C44" s="7" t="s">
         <v>901</v>
@@ -15776,25 +15789,25 @@
         <v>2022</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>1134</v>
+        <v>1129</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="J44" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K44" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="L44" s="7" t="s">
         <v>53</v>
@@ -15809,13 +15822,13 @@
         <v>53</v>
       </c>
       <c r="P44" s="7"/>
-      <c r="Q44" s="7" t="s">
-        <v>1136</v>
+      <c r="Q44" s="12" t="s">
+        <v>1131</v>
       </c>
       <c r="R44" s="7"/>
       <c r="S44" s="7"/>
       <c r="T44" s="8" t="s">
-        <v>1079</v>
+        <v>1108</v>
       </c>
       <c r="U44" s="7" t="s">
         <v>39</v>
@@ -15823,10 +15836,10 @@
     </row>
     <row r="45" spans="1:21">
       <c r="A45" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="B45" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C45" s="7" t="s">
         <v>901</v>
@@ -15835,22 +15848,22 @@
         <v>2022</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>1139</v>
+        <v>1134</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>1140</v>
+        <v>1135</v>
       </c>
       <c r="I45" s="7" t="s">
         <v>53</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="K45" s="7" t="s">
         <v>53</v>
@@ -15869,12 +15882,12 @@
       </c>
       <c r="P45" s="7"/>
       <c r="Q45" s="7" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="R45" s="7"/>
       <c r="S45" s="7"/>
       <c r="T45" s="8" t="s">
-        <v>1142</v>
+        <v>1079</v>
       </c>
       <c r="U45" s="7" t="s">
         <v>39</v>
@@ -15882,34 +15895,34 @@
     </row>
     <row r="46" spans="1:21">
       <c r="A46" t="s">
-        <v>936</v>
+        <v>942</v>
       </c>
       <c r="B46" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>901</v>
       </c>
       <c r="D46" s="7">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>1145</v>
+        <v>1139</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>1146</v>
+        <v>1140</v>
       </c>
       <c r="I46" s="7" t="s">
         <v>53</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="K46" s="7" t="s">
         <v>53</v>
@@ -15927,13 +15940,13 @@
         <v>53</v>
       </c>
       <c r="P46" s="7"/>
-      <c r="Q46" s="9" t="s">
-        <v>1147</v>
+      <c r="Q46" s="7" t="s">
+        <v>1141</v>
       </c>
       <c r="R46" s="7"/>
       <c r="S46" s="7"/>
       <c r="T46" s="8" t="s">
-        <v>1148</v>
+        <v>1142</v>
       </c>
       <c r="U46" s="7" t="s">
         <v>39</v>
@@ -15941,10 +15954,10 @@
     </row>
     <row r="47" spans="1:21">
       <c r="A47" t="s">
-        <v>930</v>
+        <v>936</v>
       </c>
       <c r="B47" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>901</v>
@@ -15953,16 +15966,16 @@
         <v>2021</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>1152</v>
+        <v>1146</v>
       </c>
       <c r="I47" s="7" t="s">
         <v>53</v>
@@ -15987,12 +16000,12 @@
       </c>
       <c r="P47" s="7"/>
       <c r="Q47" s="9" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="R47" s="7"/>
       <c r="S47" s="7"/>
       <c r="T47" s="8" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="U47" s="7" t="s">
         <v>39</v>
@@ -16000,10 +16013,10 @@
     </row>
     <row r="48" spans="1:21">
       <c r="A48" t="s">
-        <v>924</v>
+        <v>930</v>
       </c>
       <c r="B48" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>901</v>
@@ -16012,25 +16025,25 @@
         <v>2021</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J48" s="7" t="s">
         <v>53</v>
       </c>
       <c r="K48" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="L48" s="7" t="s">
         <v>53</v>
@@ -16045,13 +16058,13 @@
         <v>53</v>
       </c>
       <c r="P48" s="7"/>
-      <c r="Q48" s="12" t="s">
-        <v>1159</v>
+      <c r="Q48" s="9" t="s">
+        <v>1153</v>
       </c>
       <c r="R48" s="7"/>
       <c r="S48" s="7"/>
       <c r="T48" s="8" t="s">
-        <v>1160</v>
+        <v>1154</v>
       </c>
       <c r="U48" s="7" t="s">
         <v>39</v>
@@ -16059,10 +16072,10 @@
     </row>
     <row r="49" spans="1:21">
       <c r="A49" t="s">
-        <v>919</v>
+        <v>924</v>
       </c>
       <c r="B49" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>901</v>
@@ -16071,20 +16084,22 @@
         <v>2021</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>1162</v>
-      </c>
-      <c r="G49" s="7"/>
+        <v>1156</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>1157</v>
+      </c>
       <c r="H49" s="7" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="I49" s="7" t="s">
         <v>39</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="K49" s="7" t="s">
         <v>39</v>
@@ -16093,7 +16108,7 @@
         <v>53</v>
       </c>
       <c r="M49" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="N49" s="7" t="s">
         <v>53</v>
@@ -16102,11 +16117,13 @@
         <v>53</v>
       </c>
       <c r="P49" s="7"/>
-      <c r="Q49" s="7"/>
+      <c r="Q49" s="12" t="s">
+        <v>1159</v>
+      </c>
       <c r="R49" s="7"/>
       <c r="S49" s="7"/>
       <c r="T49" s="8" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="U49" s="7" t="s">
         <v>39</v>
@@ -16114,10 +16131,10 @@
     </row>
     <row r="50" spans="1:21">
       <c r="A50" t="s">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="B50" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>901</v>
@@ -16126,31 +16143,29 @@
         <v>2021</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>1166</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>1167</v>
-      </c>
+        <v>1162</v>
+      </c>
+      <c r="G50" s="7"/>
       <c r="H50" s="7" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="J50" s="7" t="s">
         <v>39</v>
       </c>
       <c r="K50" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="L50" s="7" t="s">
         <v>53</v>
       </c>
       <c r="M50" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="N50" s="7" t="s">
         <v>53</v>
@@ -16159,13 +16174,11 @@
         <v>53</v>
       </c>
       <c r="P50" s="7"/>
-      <c r="Q50" s="7" t="s">
-        <v>1169</v>
-      </c>
+      <c r="Q50" s="7"/>
       <c r="R50" s="7"/>
       <c r="S50" s="7"/>
       <c r="T50" s="8" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="U50" s="7" t="s">
         <v>39</v>
@@ -16173,37 +16186,37 @@
     </row>
     <row r="51" spans="1:21">
       <c r="A51" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="B51" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>901</v>
       </c>
       <c r="D51" s="7">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>1172</v>
+        <v>1166</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>1172</v>
+        <v>1166</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>1173</v>
+        <v>1167</v>
       </c>
       <c r="H51" s="7" t="s">
-        <v>1174</v>
+        <v>1168</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J51" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="L51" s="7" t="s">
         <v>53</v>
@@ -16219,12 +16232,12 @@
       </c>
       <c r="P51" s="7"/>
       <c r="Q51" s="7" t="s">
-        <v>1175</v>
+        <v>1169</v>
       </c>
       <c r="R51" s="7"/>
       <c r="S51" s="7"/>
       <c r="T51" s="8" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
       <c r="U51" s="7" t="s">
         <v>39</v>
@@ -16232,10 +16245,10 @@
     </row>
     <row r="52" spans="1:21">
       <c r="A52" t="s">
-        <v>900</v>
-      </c>
-      <c r="B52">
-        <v>1</v>
+        <v>906</v>
+      </c>
+      <c r="B52" s="7">
+        <v>2</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>901</v>
@@ -16244,25 +16257,25 @@
         <v>2020</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>1179</v>
+        <v>1173</v>
       </c>
       <c r="H52" s="7" t="s">
-        <v>1180</v>
+        <v>1174</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="J52" s="7" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="K52" s="7" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="L52" s="7" t="s">
         <v>53</v>
@@ -16277,55 +16290,117 @@
         <v>53</v>
       </c>
       <c r="P52" s="7"/>
-      <c r="Q52" s="9" t="s">
-        <v>1181</v>
+      <c r="Q52" s="7" t="s">
+        <v>1175</v>
       </c>
       <c r="R52" s="7"/>
       <c r="S52" s="7"/>
       <c r="T52" s="8" t="s">
+        <v>1176</v>
+      </c>
+      <c r="U52" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21">
+      <c r="A53" t="s">
+        <v>900</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>901</v>
+      </c>
+      <c r="D53" s="7">
+        <v>2020</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>1179</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>1180</v>
+      </c>
+      <c r="I53" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="L53" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="M53" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="N53" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="O53" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="P53" s="7"/>
+      <c r="Q53" s="9" t="s">
+        <v>1181</v>
+      </c>
+      <c r="R53" s="7"/>
+      <c r="S53" s="7"/>
+      <c r="T53" s="8" t="s">
         <v>1182</v>
       </c>
-      <c r="U52" s="7" t="s">
+      <c r="U53" s="7" t="s">
         <v>39</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="I4:O998 U4:U998">
+  <conditionalFormatting sqref="I5:O999 U5:U999">
     <cfRule type="expression" dxfId="11" priority="1">
-      <formula>I4="Yes"</formula>
+      <formula>I5="Yes"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>I4="No"</formula>
+      <formula>I5="No"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="U4:U998 I4:O998" xr:uid="{00000000-0002-0000-0500-000000000000}">
+    <dataValidation type="list" sqref="U5:U999 I5:O999" xr:uid="{00000000-0002-0000-0500-000000000000}">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="H3" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
-    <hyperlink ref="P3" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
-    <hyperlink ref="H5" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
-    <hyperlink ref="Q5" r:id="rId4" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
-    <hyperlink ref="P7" r:id="rId5" xr:uid="{00000000-0004-0000-0500-000004000000}"/>
-    <hyperlink ref="Q9" r:id="rId6" display="https://osf.io/69q84/" xr:uid="{00000000-0004-0000-0500-000005000000}"/>
-    <hyperlink ref="S9" r:id="rId7" display="https://osf.io/69q84/" xr:uid="{00000000-0004-0000-0500-000006000000}"/>
-    <hyperlink ref="P12" r:id="rId8" xr:uid="{00000000-0004-0000-0500-000007000000}"/>
-    <hyperlink ref="Q42" r:id="rId9" xr:uid="{00000000-0004-0000-0500-000008000000}"/>
-    <hyperlink ref="Q43" r:id="rId10" xr:uid="{00000000-0004-0000-0500-000009000000}"/>
-    <hyperlink ref="Q46" r:id="rId11" xr:uid="{00000000-0004-0000-0500-00000A000000}"/>
-    <hyperlink ref="Q47" r:id="rId12" xr:uid="{00000000-0004-0000-0500-00000B000000}"/>
-    <hyperlink ref="Q48" r:id="rId13" xr:uid="{00000000-0004-0000-0500-00000C000000}"/>
-    <hyperlink ref="Q52" r:id="rId14" xr:uid="{00000000-0004-0000-0500-00000D000000}"/>
-    <hyperlink ref="P8" r:id="rId15" xr:uid="{1FEC8C46-8B4A-4709-8A05-15668E1BE58C}"/>
-    <hyperlink ref="H2" r:id="rId16" xr:uid="{B218345E-5C1C-47AC-AB7C-B2437AC8A8C2}"/>
+    <hyperlink ref="H4" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="P4" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="H6" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="Q6" r:id="rId4" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
+    <hyperlink ref="P8" r:id="rId5" xr:uid="{00000000-0004-0000-0500-000004000000}"/>
+    <hyperlink ref="Q10" r:id="rId6" display="https://osf.io/69q84/" xr:uid="{00000000-0004-0000-0500-000005000000}"/>
+    <hyperlink ref="S10" r:id="rId7" display="https://osf.io/69q84/" xr:uid="{00000000-0004-0000-0500-000006000000}"/>
+    <hyperlink ref="P13" r:id="rId8" xr:uid="{00000000-0004-0000-0500-000007000000}"/>
+    <hyperlink ref="Q43" r:id="rId9" xr:uid="{00000000-0004-0000-0500-000008000000}"/>
+    <hyperlink ref="Q44" r:id="rId10" xr:uid="{00000000-0004-0000-0500-000009000000}"/>
+    <hyperlink ref="Q47" r:id="rId11" xr:uid="{00000000-0004-0000-0500-00000A000000}"/>
+    <hyperlink ref="Q48" r:id="rId12" xr:uid="{00000000-0004-0000-0500-00000B000000}"/>
+    <hyperlink ref="Q49" r:id="rId13" xr:uid="{00000000-0004-0000-0500-00000C000000}"/>
+    <hyperlink ref="Q53" r:id="rId14" xr:uid="{00000000-0004-0000-0500-00000D000000}"/>
+    <hyperlink ref="P9" r:id="rId15" xr:uid="{1FEC8C46-8B4A-4709-8A05-15668E1BE58C}"/>
+    <hyperlink ref="H3" r:id="rId16" xr:uid="{B218345E-5C1C-47AC-AB7C-B2437AC8A8C2}"/>
+    <hyperlink ref="H2" r:id="rId17" xr:uid="{6E123998-D773-43AA-BB55-58A0C0F734F5}"/>
+    <hyperlink ref="Q2" r:id="rId18" xr:uid="{C528454D-59DE-4F5E-8BC8-723E549633BE}"/>
+    <hyperlink ref="S2" r:id="rId19" xr:uid="{C4078AFC-EA82-47D8-9303-69484BE94F05}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <tableParts count="1">
-    <tablePart r:id="rId17"/>
+    <tablePart r:id="rId20"/>
   </tableParts>
 </worksheet>
 </file>
